--- a/data/xlsx/sbce_config_esxi_ems1_sbce1_ems2_sbce2_template.xlsx
+++ b/data/xlsx/sbce_config_esxi_ems1_sbce1_ems2_sbce2_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sszokoly\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE828A1A-8258-4DA9-B2FE-B11331190FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9DD4D8-2EBD-45F3-A758-102887598E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EMS1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="137">
   <si>
     <t>platform_type</t>
   </si>
@@ -419,9 +419,6 @@
     <t>SBCE</t>
   </si>
   <si>
-    <t>sbce</t>
-  </si>
-  <si>
     <t>10.10.48.11</t>
   </si>
   <si>
@@ -447,6 +444,12 @@
   </si>
   <si>
     <t>10.10.48.17</t>
+  </si>
+  <si>
+    <t>sbce_site_2</t>
+  </si>
+  <si>
+    <t>sbce_site_1</t>
   </si>
 </sst>
 </file>
@@ -2109,7 +2112,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>26</v>
@@ -2140,7 +2143,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>34</v>
@@ -2417,7 +2420,7 @@
         <v>101</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>102</v>
@@ -2428,7 +2431,7 @@
         <v>103</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>104</v>
@@ -2468,7 +2471,7 @@
         <v>111</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>112</v>
@@ -2501,7 +2504,7 @@
         <v>117</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>118</v>
@@ -2741,7 +2744,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
@@ -2763,7 +2766,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>22</v>
@@ -2785,7 +2788,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>26</v>
@@ -2818,7 +2821,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>34</v>
@@ -3164,112 +3167,112 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="21" priority="22">
+    <cfRule type="expression" dxfId="38" priority="22">
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="expression" dxfId="20" priority="21">
+    <cfRule type="expression" dxfId="37" priority="21">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="36" priority="1">
       <formula>B10&lt;&gt;"EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="18" priority="20">
+    <cfRule type="expression" dxfId="35" priority="20">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="34" priority="19">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="16" priority="18">
+    <cfRule type="expression" dxfId="33" priority="18">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="expression" dxfId="15" priority="17">
+    <cfRule type="expression" dxfId="32" priority="17">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="14" priority="16">
+    <cfRule type="expression" dxfId="31" priority="16">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="expression" dxfId="13" priority="15">
+    <cfRule type="expression" dxfId="30" priority="15">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="expression" dxfId="12" priority="14">
+    <cfRule type="expression" dxfId="29" priority="14">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="expression" dxfId="11" priority="13">
+    <cfRule type="expression" dxfId="28" priority="13">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39">
-    <cfRule type="expression" dxfId="10" priority="12">
+    <cfRule type="expression" dxfId="27" priority="12">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B40">
-    <cfRule type="expression" dxfId="9" priority="11">
+    <cfRule type="expression" dxfId="26" priority="11">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B41">
-    <cfRule type="expression" dxfId="8" priority="10">
+    <cfRule type="expression" dxfId="25" priority="10">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="expression" dxfId="7" priority="9">
+    <cfRule type="expression" dxfId="24" priority="9">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43">
-    <cfRule type="expression" dxfId="6" priority="8">
+    <cfRule type="expression" dxfId="23" priority="8">
       <formula>B10&lt;&gt;"SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="22" priority="7">
       <formula>B10&lt;&gt;"SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="expression" dxfId="4" priority="6">
+    <cfRule type="expression" dxfId="21" priority="6">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="20" priority="5">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="19" priority="4">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="18" priority="3">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B49">
-    <cfRule type="expression" dxfId="0" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3417,7 +3420,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>17</v>
@@ -3439,7 +3442,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>22</v>
@@ -3461,7 +3464,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>26</v>
@@ -3492,7 +3495,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>34</v>
@@ -3661,7 +3664,7 @@
         <v>77</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>78</v>
@@ -3769,7 +3772,7 @@
         <v>101</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>102</v>
@@ -3780,7 +3783,7 @@
         <v>103</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>104</v>
@@ -3820,7 +3823,7 @@
         <v>111</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>112</v>
@@ -3853,7 +3856,7 @@
         <v>117</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>118</v>
@@ -3861,87 +3864,87 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="38" priority="18">
+    <cfRule type="expression" dxfId="16" priority="18">
       <formula>B1="KVM"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="expression" dxfId="37" priority="17">
+    <cfRule type="expression" dxfId="15" priority="17">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B13">
-    <cfRule type="expression" dxfId="36" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>B10&lt;&gt;"EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B21">
-    <cfRule type="expression" dxfId="35" priority="16">
+    <cfRule type="expression" dxfId="13" priority="16">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22">
-    <cfRule type="expression" dxfId="34" priority="15">
+    <cfRule type="expression" dxfId="12" priority="15">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" dxfId="33" priority="14">
+    <cfRule type="expression" dxfId="11" priority="14">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24">
-    <cfRule type="expression" dxfId="32" priority="13">
+    <cfRule type="expression" dxfId="10" priority="13">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25">
-    <cfRule type="expression" dxfId="31" priority="12">
+    <cfRule type="expression" dxfId="9" priority="12">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="expression" dxfId="30" priority="11">
+    <cfRule type="expression" dxfId="8" priority="11">
       <formula>B10="SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="expression" dxfId="29" priority="10">
+    <cfRule type="expression" dxfId="7" priority="10">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="expression" dxfId="28" priority="9">
+    <cfRule type="expression" dxfId="6" priority="9">
       <formula>B10="EMS+SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="expression" dxfId="27" priority="8">
+    <cfRule type="expression" dxfId="5" priority="8">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B43:B44">
-    <cfRule type="expression" dxfId="26" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>B10&lt;&gt;"SBCE"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="expression" dxfId="25" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="expression" dxfId="24" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B47">
-    <cfRule type="expression" dxfId="23" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B48:B49">
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>B10="EMS"</formula>
     </cfRule>
   </conditionalFormatting>
